--- a/B8 Unit Cell - k_inf/modr-fuel-ratio.xlsx
+++ b/B8 Unit Cell - k_inf/modr-fuel-ratio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MCNP\haigerloch-modr-fuel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MCNP\b8pile\B8 Unit Cell - k_inf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479710F9-89E7-4635-8E7A-9D5340A6300D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B4A31E-EB9B-47AF-BE3F-AFF83A0B854A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -129,8 +129,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+  <numFmts count="2">
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
   </numFmts>
@@ -225,7 +224,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -236,7 +234,8 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -314,7 +313,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>13.302</c:v>
@@ -325,7 +324,7 @@
                 <c:pt idx="2">
                   <c:v>14.2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.0">
+                <c:pt idx="3">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
@@ -340,7 +339,7 @@
                 <c:pt idx="7">
                   <c:v>18.2</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0.0">
+                <c:pt idx="8">
                   <c:v>18.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
@@ -463,7 +462,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>13.302</c:v>
@@ -474,7 +473,7 @@
                 <c:pt idx="2">
                   <c:v>14.2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.0">
+                <c:pt idx="3">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
@@ -489,7 +488,7 @@
                 <c:pt idx="7">
                   <c:v>18.2</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0.0">
+                <c:pt idx="8">
                   <c:v>18.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
@@ -612,7 +611,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>13.302</c:v>
@@ -623,7 +622,7 @@
                 <c:pt idx="2">
                   <c:v>14.2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.0">
+                <c:pt idx="3">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
@@ -638,7 +637,7 @@
                 <c:pt idx="7">
                   <c:v>18.2</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0.0">
+                <c:pt idx="8">
                   <c:v>18.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
@@ -761,7 +760,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$18</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>13.302</c:v>
@@ -772,7 +771,7 @@
                 <c:pt idx="2">
                   <c:v>14.2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.0">
+                <c:pt idx="3">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
@@ -787,7 +786,7 @@
                 <c:pt idx="7">
                   <c:v>18.2</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0.0">
+                <c:pt idx="8">
                   <c:v>18.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
@@ -910,7 +909,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$22</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>13.302</c:v>
@@ -921,7 +920,7 @@
                 <c:pt idx="2">
                   <c:v>14.2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.0">
+                <c:pt idx="3">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
@@ -936,7 +935,7 @@
                 <c:pt idx="7">
                   <c:v>18.2</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0.0">
+                <c:pt idx="8">
                   <c:v>18.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
@@ -1085,7 +1084,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1200,6 +1199,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1207,7 +1207,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1321,7 +1320,7 @@
             <c:numRef>
               <c:f>Sheet1!$E$3:$E$11</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>13.302</c:v>
@@ -1332,7 +1331,7 @@
                 <c:pt idx="2">
                   <c:v>14.2</c:v>
                 </c:pt>
-                <c:pt idx="3" formatCode="0.0">
+                <c:pt idx="3">
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="4">
@@ -1347,7 +1346,7 @@
                 <c:pt idx="7">
                   <c:v>18.2</c:v>
                 </c:pt>
-                <c:pt idx="8" formatCode="0.0">
+                <c:pt idx="8">
                   <c:v>18.600000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1455,9 +1454,9 @@
             <c:numRef>
               <c:f>Sheet1!$E$11:$E$20</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="10"/>
-                <c:pt idx="0" formatCode="0.0">
+                <c:pt idx="0">
                   <c:v>18.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -1674,7 +1673,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1867,6 +1866,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1874,7 +1874,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -3395,16 +3394,16 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -3455,27 +3454,27 @@
       <c r="P2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="Q2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="T2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="V2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>1787.75</v>
       </c>
       <c r="B3">
@@ -3486,45 +3485,45 @@
         <f t="shared" ref="C3:C13" si="0">A3-D3</f>
         <v>1662.75</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>125</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="15">
         <f>C3/D3</f>
         <v>13.302</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <f>1.12309-0.00715</f>
         <v>1.1159399999999999</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>87.4</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>4.3600000000000003</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>8.24</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>7.7593799999999997E-3</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>8.9868599999999993E-3</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="9">
         <v>5.9162099999999999E-3</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <v>7.6359100000000001E-3</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>2.7750699999999998E-5</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="9">
         <v>3.0204300000000001E-5</v>
       </c>
       <c r="Q3">
@@ -3553,7 +3552,7 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>1800</v>
       </c>
       <c r="B4">
@@ -3564,45 +3563,45 @@
         <f t="shared" si="0"/>
         <v>1675</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>125</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="15">
         <f t="shared" ref="E4:E9" si="2">C4/D4</f>
         <v>13.4</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <f>1.12367-0.00715</f>
         <v>1.11652</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>1E-4</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>87.44</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>4.34</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>8.2100000000000009</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>7.7631499999999999E-3</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>8.9863100000000008E-3</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>5.9188599999999997E-3</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>7.6301700000000004E-3</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>2.7781400000000001E-5</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="9">
         <v>3.0216899999999999E-5</v>
       </c>
       <c r="Q4">
@@ -3631,7 +3630,7 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>1900</v>
       </c>
       <c r="B5">
@@ -3642,45 +3641,45 @@
         <f t="shared" si="0"/>
         <v>1775</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>125</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="15">
         <f t="shared" si="2"/>
         <v>14.2</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <f>1.12701-0.00715</f>
         <v>1.1198600000000001</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>87.81</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>4.1100000000000003</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>8.07</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <v>7.8240500000000008E-3</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="9">
         <v>9.0165100000000001E-3</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="9">
         <v>5.9634400000000004E-3</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="9">
         <v>7.60379E-3</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="9">
         <v>2.8185900000000001E-5</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="9">
         <v>3.0504100000000002E-5</v>
       </c>
       <c r="Q5">
@@ -3709,7 +3708,7 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>2000</v>
       </c>
       <c r="B6">
@@ -3720,45 +3719,45 @@
         <f t="shared" si="0"/>
         <v>1875</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>125</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="15">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <f>1.12962-0.00715</f>
         <v>1.1224700000000001</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>88.12</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>3.92</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>7.96</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>7.8720700000000001E-3</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>9.0379999999999992E-3</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>5.9983199999999997E-3</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
         <v>7.5770500000000001E-3</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="9">
         <v>2.85178E-5</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="9">
         <v>3.0731200000000001E-5</v>
       </c>
       <c r="Q6">
@@ -3787,7 +3786,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>2100</v>
       </c>
       <c r="B7">
@@ -3798,52 +3797,52 @@
         <f t="shared" si="0"/>
         <v>1975</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>125</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="15">
         <f t="shared" si="2"/>
         <v>15.8</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <f>1.13139-0.00715</f>
         <v>1.1242399999999999</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>88.42</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>3.74</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>7.85</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <v>7.9099600000000006E-3</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>9.0497200000000007E-3</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="9">
         <v>6.02573E-3</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="9">
         <v>7.5471499999999999E-3</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="9">
         <v>2.8816700000000001E-5</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="9">
         <v>3.0928600000000001E-5</v>
       </c>
       <c r="Q7">
         <f t="shared" si="3"/>
         <v>1.0815616721561248</v>
       </c>
-      <c r="R7" s="13">
+      <c r="R7" s="12">
         <f t="shared" si="4"/>
         <v>1.126172298881269</v>
       </c>
@@ -3865,7 +3864,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <v>2200</v>
       </c>
       <c r="B8">
@@ -3876,45 +3875,45 @@
         <f t="shared" si="0"/>
         <v>2075</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>125</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="15">
         <f t="shared" si="2"/>
         <v>16.600000000000001</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <f>1.1327-0.00715</f>
         <v>1.1255500000000001</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>88.69</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="8">
         <v>3.56</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>7.75</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="9">
         <v>7.9453200000000005E-3</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="9">
         <v>9.0619399999999992E-3</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="9">
         <v>6.0512099999999996E-3</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="9">
         <v>7.5199100000000003E-3</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="9">
         <v>2.9098499999999999E-5</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="9">
         <v>3.1119199999999998E-5</v>
       </c>
       <c r="Q8">
@@ -3943,7 +3942,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <v>2300</v>
       </c>
       <c r="B9">
@@ -3954,45 +3953,45 @@
         <f t="shared" si="0"/>
         <v>2175</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>125</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="15">
         <f t="shared" si="2"/>
         <v>17.399999999999999</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <f>1.13376-0.00715</f>
         <v>1.1266100000000001</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>88.91</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="8">
         <v>3.42</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>7.67</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <v>7.9746499999999998E-3</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <v>9.07086E-3</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <v>6.0722600000000003E-3</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="9">
         <v>7.4923200000000002E-3</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9" s="9">
         <v>2.9344900000000001E-5</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="9">
         <v>3.1286499999999999E-5</v>
       </c>
       <c r="Q9">
@@ -4021,7 +4020,7 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <v>2400</v>
       </c>
       <c r="B10">
@@ -4032,48 +4031,48 @@
         <f t="shared" si="0"/>
         <v>2275</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>125</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="15">
         <f>C10/D10</f>
         <v>18.2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <f>1.13417-0.00715</f>
         <v>1.1270199999999999</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="8">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>89.12</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="8">
         <v>3.29</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>7.6</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="9">
         <v>7.9980699999999995E-3</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="9">
         <v>9.0750399999999995E-3</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="9">
         <v>6.0889300000000002E-3</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10" s="9">
         <v>7.4668299999999998E-3</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10" s="9">
         <v>2.9565900000000001E-5</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="9">
         <v>3.1432500000000001E-5</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="12">
         <f t="shared" si="3"/>
         <v>1.0847372958965205</v>
       </c>
@@ -4133,22 +4132,22 @@
       <c r="J11" s="2">
         <v>7.56</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>8.0059699999999994E-3</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="13">
         <v>9.0735399999999997E-3</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="13">
         <v>6.0944199999999997E-3</v>
       </c>
-      <c r="N11" s="14">
+      <c r="N11" s="13">
         <v>7.4504799999999998E-3</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="13">
         <v>2.96549E-5</v>
       </c>
-      <c r="P11" s="14">
+      <c r="P11" s="13">
         <v>3.1486899999999998E-5</v>
       </c>
       <c r="Q11">
@@ -4177,7 +4176,7 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <v>2500</v>
       </c>
       <c r="B12">
@@ -4188,45 +4187,45 @@
         <f t="shared" si="0"/>
         <v>2375</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>125</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="15">
         <f t="shared" ref="E12:E14" si="12">C12/D12</f>
         <v>19</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <f>1.13416-0.00715</f>
         <v>1.1270100000000001</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="8">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>89.32</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="8">
         <v>3.15</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>7.53</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="9">
         <v>8.0138599999999994E-3</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="9">
         <v>9.0724800000000008E-3</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="9">
         <v>6.0999100000000001E-3</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="9">
         <v>7.4364899999999996E-3</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="9">
         <v>2.9756699999999999E-5</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="9">
         <v>3.1552900000000001E-5</v>
       </c>
       <c r="Q12">
@@ -4255,7 +4254,7 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>2600</v>
       </c>
       <c r="B13">
@@ -4266,45 +4265,45 @@
         <f t="shared" si="0"/>
         <v>2475</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>125</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="15">
         <f t="shared" si="12"/>
         <v>19.8</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <f>1.13384-0.00715</f>
         <v>1.12669</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>89.49</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>3.05</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>7.46</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="9">
         <v>8.0302099999999994E-3</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="9">
         <v>9.0722700000000003E-3</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="9">
         <v>6.1114300000000002E-3</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="9">
         <v>7.4101999999999996E-3</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="9">
         <v>2.9938699999999998E-5</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="9">
         <v>3.1671000000000002E-5</v>
       </c>
       <c r="Q13">
@@ -4333,7 +4332,7 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <v>2700</v>
       </c>
       <c r="B14">
@@ -4344,45 +4343,45 @@
         <f t="shared" ref="C14:C20" si="14">A14-D14</f>
         <v>2575</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>125</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="15">
         <f t="shared" si="12"/>
         <v>20.6</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <f>1.1332-0.00715</f>
         <v>1.12605</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>89.65</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="8">
         <v>2.94</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <v>7.41</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="9">
         <v>8.0402900000000003E-3</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="9">
         <v>9.0665099999999998E-3</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="9">
         <v>6.1180599999999998E-3</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="9">
         <v>7.3822699999999998E-3</v>
       </c>
-      <c r="O14" s="10">
+      <c r="O14" s="9">
         <v>3.0100700000000001E-5</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="9">
         <v>3.1770899999999998E-5</v>
       </c>
       <c r="Q14">
@@ -4411,7 +4410,7 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>2800</v>
       </c>
       <c r="B15">
@@ -4422,45 +4421,45 @@
         <f t="shared" si="14"/>
         <v>2675</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>125</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="15">
         <f>C15/D15</f>
         <v>21.4</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <f>1.1325-0.00715</f>
         <v>1.1253500000000001</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>89.79</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>2.84</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>7.36</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="9">
         <v>8.0475800000000004E-3</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="9">
         <v>9.0594899999999999E-3</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="9">
         <v>6.1228100000000002E-3</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="9">
         <v>7.3545499999999996E-3</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="9">
         <v>3.0250600000000001E-5</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="9">
         <v>3.18648E-5</v>
       </c>
       <c r="Q15">
@@ -4489,7 +4488,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>2900</v>
       </c>
       <c r="B16">
@@ -4500,45 +4499,45 @@
         <f t="shared" si="14"/>
         <v>2775</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>125</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="15">
         <f t="shared" ref="E16:E17" si="15">C16/D16</f>
         <v>22.2</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <f>1.13143-0.00715</f>
         <v>1.1242799999999999</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>89.93</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>2.75</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <v>7.32</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="9">
         <v>8.0519100000000007E-3</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="9">
         <v>9.0505199999999994E-3</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="9">
         <v>6.1253699999999998E-3</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="9">
         <v>7.3261400000000001E-3</v>
       </c>
-      <c r="O16" s="10">
+      <c r="O16" s="9">
         <v>3.03722E-5</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="9">
         <v>3.19388E-5</v>
       </c>
       <c r="Q16">
@@ -4567,7 +4566,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>3000</v>
       </c>
       <c r="B17">
@@ -4578,45 +4577,45 @@
         <f t="shared" si="14"/>
         <v>2875</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>125</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="15">
         <f t="shared" si="15"/>
         <v>23</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <f>1.1301-0.00715</f>
         <v>1.1229500000000001</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>9.0000000000000006E-5</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>90.05</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="8">
         <v>2.67</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>7.28</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
         <v>8.0527700000000008E-3</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>9.0388199999999995E-3</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>6.1252800000000003E-3</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="9">
         <v>7.2990299999999998E-3</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="9">
         <v>3.0475900000000001E-5</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="9">
         <v>3.1990599999999998E-5</v>
       </c>
       <c r="Q17">
@@ -4645,7 +4644,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <v>3100</v>
       </c>
       <c r="B18">
@@ -4656,45 +4655,45 @@
         <f t="shared" si="14"/>
         <v>2975</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>125</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="15">
         <f>C18/D18</f>
         <v>23.8</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <f>1.12871-0.00715</f>
         <v>1.1215600000000001</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>90.18</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="8">
         <v>2.58</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>7.24</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="9">
         <v>8.0567799999999995E-3</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>9.0302799999999999E-3</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <v>6.1276100000000003E-3</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <v>7.2742299999999996E-3</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="9">
         <v>3.0578699999999999E-5</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="9">
         <v>3.2046499999999999E-5</v>
       </c>
       <c r="Q18">
@@ -4723,7 +4722,7 @@
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <v>3200</v>
       </c>
       <c r="B19">
@@ -4734,45 +4733,45 @@
         <f t="shared" si="14"/>
         <v>3075</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>125</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="15">
         <f t="shared" ref="E19:E21" si="16">C19/D19</f>
         <v>24.6</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <f>1.12706-0.00715</f>
         <v>1.11991</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>6.9999999999999994E-5</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>90.28</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <v>2.5099999999999998</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="8">
         <v>7.21</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="9">
         <v>8.0523299999999999E-3</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>9.0147100000000004E-3</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="9">
         <v>6.1235500000000002E-3</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="9">
         <v>7.2455499999999999E-3</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O19" s="9">
         <v>3.0666000000000001E-5</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="9">
         <v>3.2091400000000002E-5</v>
       </c>
       <c r="Q19">
@@ -4801,7 +4800,7 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+      <c r="A20" s="7">
         <v>3300</v>
       </c>
       <c r="B20">
@@ -4812,45 +4811,45 @@
         <f t="shared" si="14"/>
         <v>3175</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>125</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="15">
         <f t="shared" si="16"/>
         <v>25.4</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <f>1.12516-0.00715</f>
         <v>1.1180099999999999</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>8.0000000000000007E-5</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>90.37</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <v>2.44</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="8">
         <v>7.19</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="9">
         <v>8.0503399999999996E-3</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>9.0020399999999993E-3</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="9">
         <v>6.1215499999999999E-3</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="9">
         <v>7.2201499999999998E-3</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="9">
         <v>3.0752700000000001E-5</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="9">
         <v>3.2136299999999999E-5</v>
       </c>
       <c r="Q20">
@@ -4879,7 +4878,7 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <v>3400</v>
       </c>
       <c r="B21">
@@ -4890,24 +4889,24 @@
         <f t="shared" ref="C21:C22" si="18">A21-D21</f>
         <v>3275</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>125</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="15">
         <f t="shared" si="16"/>
         <v>26.2</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
       <c r="Q21" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
@@ -4934,7 +4933,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+      <c r="A22" s="7">
         <v>3500</v>
       </c>
       <c r="B22">
@@ -4945,24 +4944,24 @@
         <f t="shared" si="18"/>
         <v>3375</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>125</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="15">
         <f>C22/D22</f>
         <v>27</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
       <c r="Q22" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>

--- a/B8 Unit Cell - k_inf/modr-fuel-ratio.xlsx
+++ b/B8 Unit Cell - k_inf/modr-fuel-ratio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MCNP\haigerloch-modr-fuel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MCNP\b8pile\B8 Unit Cell - k_inf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479710F9-89E7-4635-8E7A-9D5340A6300D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365CB527-59C6-4275-824D-C97E18E018E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1200,6 +1200,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1207,7 +1208,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1776,7 +1776,7 @@
                     <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:rPr>
-                  <a:t>inf</a:t>
+                  <a:t>∞</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US">
@@ -1867,6 +1867,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1874,7 +1875,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
